--- a/data/trans_bre/P44-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P44-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,5</t>
+          <t>-4,24; 3,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 2,75</t>
+          <t>-7,43; 2,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 2,42</t>
+          <t>-8,53; 2,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 97,7</t>
+          <t>-55,17; 106,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,65; 36,56</t>
+          <t>-53,08; 38,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 8,54</t>
+          <t>-24,49; 8,86</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 4,86</t>
+          <t>-4,03; 5,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,24</t>
+          <t>-6,75; 1,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,82; -4,69</t>
+          <t>-55,23; -4,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 78,87</t>
+          <t>-33,96; 88,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,84; 17,93</t>
+          <t>-55,8; 17,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,44; -12,85</t>
+          <t>-67,62; -13,24</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 2,54</t>
+          <t>-8,82; 3,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 0,16</t>
+          <t>-9,39; 0,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,92; -7,17</t>
+          <t>-33,56; -6,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 32,57</t>
+          <t>-57,46; 42,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 4,12</t>
+          <t>-67,32; 3,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,38; -21,46</t>
+          <t>-87,52; -22,0</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,1; -1,82</t>
+          <t>-10,44; -1,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -2,98</t>
+          <t>-11,28; -2,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -3,99</t>
+          <t>-14,12; -3,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,32; -18,87</t>
+          <t>-70,64; -16,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,16; -25,22</t>
+          <t>-67,16; -24,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,8; -9,81</t>
+          <t>-30,39; -9,54</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 0,09</t>
+          <t>-4,39; 0,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; -2,17</t>
+          <t>-6,49; -2,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,06; -8,19</t>
+          <t>-44,62; -7,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 1,93</t>
+          <t>-40,43; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,88; -19,52</t>
+          <t>-49,51; -18,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,99; -22,27</t>
+          <t>-70,53; -21,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P44-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P44-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-2,76</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-10,2%</t>
+          <t>-8,92%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 3,69</t>
+          <t>-4,26; 3,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 2,79</t>
+          <t>-7,56; 2,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 2,43</t>
+          <t>-8,61; 2,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-55,17; 106,08</t>
+          <t>-54,49; 94,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,08; 38,45</t>
+          <t>-55,06; 29,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 8,86</t>
+          <t>-24,42; 11,21</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-30,47</t>
+          <t>-6,01</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-50,66%</t>
+          <t>-16,82%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 5,52</t>
+          <t>-3,33; 5,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 1,08</t>
+          <t>-6,31; 1,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,23; -4,64</t>
+          <t>-11,34; -0,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,96; 88,62</t>
+          <t>-30,5; 95,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 17,33</t>
+          <t>-52,6; 17,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,62; -13,24</t>
+          <t>-29,16; -0,94</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-18,97</t>
+          <t>-7,37</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-56,76%</t>
+          <t>-22,61%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 3,16</t>
+          <t>-9,3; 2,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 0,25</t>
+          <t>-9,59; 0,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,56; -6,97</t>
+          <t>-13,38; -1,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-57,46; 42,87</t>
+          <t>-56,53; 39,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,32; 3,44</t>
+          <t>-66,62; 3,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-87,52; -22,0</t>
+          <t>-37,17; -4,69</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-8,88</t>
+          <t>-7,73</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-20,48%</t>
+          <t>-18,04%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,44; -1,62</t>
+          <t>-10,62; -1,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -2,9</t>
+          <t>-11,47; -2,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -3,75</t>
+          <t>-12,75; -3,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,64; -16,5</t>
+          <t>-68,67; -14,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,16; -24,29</t>
+          <t>-66,19; -22,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -9,54</t>
+          <t>-27,81; -7,63</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-19,13</t>
+          <t>-5,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-41,9%</t>
+          <t>-16,18%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,09</t>
+          <t>-4,35; 0,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -2,01</t>
+          <t>-6,55; -2,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-44,62; -7,68</t>
+          <t>-8,49; -3,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 1,06</t>
+          <t>-39,97; 3,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -18,48</t>
+          <t>-50,87; -19,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-70,53; -21,23</t>
+          <t>-22,73; -8,63</t>
         </is>
       </c>
     </row>
